--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -317,10 +317,10 @@
     <t>亚克东技能</t>
   </si>
   <si>
-    <t>HuntingConfig.Enum.ELuckyType</t>
-  </si>
-  <si>
-    <t>幸运仪式类型</t>
+    <t>HuntingConfig.Enum.ELuckyBuffType</t>
+  </si>
+  <si>
+    <t>幸运仪式增益类型</t>
   </si>
   <si>
     <t>None</t>
@@ -332,10 +332,10 @@
     <t>MoreMeat</t>
   </si>
   <si>
-    <t>爆肉加成</t>
-  </si>
-  <si>
-    <t>SpecialBullet</t>
+    <t>更多大肉</t>
+  </si>
+  <si>
+    <t>StartSpecialBullet</t>
   </si>
   <si>
     <t>开局特殊子弹</t>
@@ -356,7 +356,52 @@
     <t>HighTierSpawn</t>
   </si>
   <si>
-    <t>高阶派发加成</t>
+    <t>高阶派发</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyBuffStrengthType</t>
+  </si>
+  <si>
+    <t>幸运仪式增益强度类型</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>弱档</t>
+  </si>
+  <si>
+    <t>中档</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>强档</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyGiftType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幸运仪式礼包类型 </t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>初级礼包</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>中级礼包</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>高级礼包</t>
   </si>
   <si>
     <t>HuntingConfig.Enum.EQuestType</t>
@@ -1115,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1155,19 +1200,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1492,7 +1534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1500,7 +1542,7 @@
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="17.75" customWidth="1"/>
+    <col min="6" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="5.375" customWidth="1"/>
     <col min="8" max="8" width="22.125" customWidth="1"/>
     <col min="9" max="9" width="16.375" customWidth="1"/>
@@ -1598,7 +1640,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" ht="17.25" spans="1:12">
+    <row r="4" ht="17.25" customHeight="1" spans="1:12">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
         <v>21</v>
@@ -1628,7 +1670,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" ht="17.25" spans="1:12">
+    <row r="5" ht="17.25" customHeight="1" spans="1:12">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
@@ -1648,7 +1690,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" ht="17.25" spans="1:12">
+    <row r="6" ht="17.25" customHeight="1" spans="1:12">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1668,7 +1710,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
+    <row r="7" ht="17.25" customHeight="1" spans="1:12">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -1688,7 +1730,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" ht="17.25" customHeight="1" spans="1:12">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -1708,7 +1750,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" customHeight="1" spans="1:12">
+    <row r="9" ht="17.25" customHeight="1" spans="1:12">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -1728,7 +1770,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" ht="17.25" spans="1:12">
+    <row r="10" ht="17.25" customHeight="1" spans="1:12">
       <c r="A10" s="8"/>
       <c r="B10" s="4" t="s">
         <v>36</v>
@@ -1758,7 +1800,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" ht="17.25" spans="1:12">
+    <row r="11" ht="17.25" customHeight="1" spans="1:12">
       <c r="A11" s="8"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -1778,7 +1820,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" ht="17.25" spans="1:12">
+    <row r="12" ht="17.25" customHeight="1" spans="1:12">
       <c r="A12" s="8"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
@@ -1798,7 +1840,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" ht="17.25" spans="1:12">
+    <row r="13" ht="17.25" customHeight="1" spans="1:12">
       <c r="A13" s="8"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1818,7 +1860,7 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" ht="17.25" spans="1:12">
+    <row r="14" ht="17.25" customHeight="1" spans="1:12">
       <c r="A14" s="8"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
@@ -1838,7 +1880,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" ht="17.25" spans="1:12">
+    <row r="15" ht="17.25" customHeight="1" spans="1:12">
       <c r="A15" s="8"/>
       <c r="B15" s="6" t="s">
         <v>48</v>
@@ -1868,7 +1910,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" ht="17.25" spans="1:12">
+    <row r="16" ht="17.25" customHeight="1" spans="1:12">
       <c r="A16" s="8"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -1888,7 +1930,7 @@
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" ht="17.25" spans="1:12">
+    <row r="17" ht="17.25" customHeight="1" spans="1:12">
       <c r="A17" s="8"/>
       <c r="B17" s="6"/>
       <c r="C17" s="5"/>
@@ -1908,7 +1950,7 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" ht="17.25" spans="1:12">
+    <row r="18" ht="17.25" customHeight="1" spans="1:12">
       <c r="A18" s="8"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -1928,7 +1970,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" spans="1:12">
+    <row r="19" ht="17.25" customHeight="1" spans="1:12">
       <c r="B19" s="6" t="s">
         <v>58</v>
       </c>
@@ -1955,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="17.25" spans="1:12">
+    <row r="20" ht="17.25" customHeight="1" spans="1:12">
       <c r="B20" s="6"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1972,7 +2014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.25" spans="1:12">
+    <row r="21" ht="17.25" customHeight="1" spans="1:12">
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1989,7 +2031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" ht="17.25" spans="1:12">
+    <row r="22" ht="17.25" customHeight="1" spans="1:12">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -2006,7 +2048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="17.25" spans="1:12">
+    <row r="23" ht="17.25" customHeight="1" spans="1:12">
       <c r="B23" s="6" t="s">
         <v>68</v>
       </c>
@@ -2033,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="17.25" spans="1:12">
+    <row r="24" ht="17.25" customHeight="1" spans="1:12">
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2050,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.25" spans="1:12">
+    <row r="25" ht="17.25" customHeight="1" spans="1:12">
       <c r="B25" s="6"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2067,7 +2109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17.25" spans="1:12">
+    <row r="26" ht="17.25" customHeight="1" spans="1:12">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2084,7 +2126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="17.25" spans="1:12">
+    <row r="27" ht="17.25" customHeight="1" spans="1:12">
       <c r="B27" s="11" t="s">
         <v>78</v>
       </c>
@@ -2111,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="17.25" spans="1:12">
+    <row r="28" ht="17.25" customHeight="1" spans="1:12">
       <c r="B28" s="11"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2128,7 +2170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="17.25" spans="1:12">
+    <row r="29" ht="17.25" customHeight="1" spans="1:12">
       <c r="B29" s="11" t="s">
         <v>84</v>
       </c>
@@ -2155,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="17.25" spans="1:12">
+    <row r="30" ht="17.25" customHeight="1" spans="1:12">
       <c r="B30" s="11"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2172,7 +2214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="17.25" spans="1:12">
+    <row r="31" ht="17.25" customHeight="1" spans="1:12">
       <c r="B31" s="11"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2189,7 +2231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="17.25" spans="1:12">
+    <row r="32" ht="17.25" customHeight="1" spans="1:12">
       <c r="B32" s="11"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2206,7 +2248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" ht="17.25" spans="2:10">
+    <row r="33" ht="17.25" customHeight="1" spans="2:10">
       <c r="B33" s="11"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -2223,7 +2265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" ht="17.25" spans="2:10">
+    <row r="34" ht="17.25" customHeight="1" spans="2:10">
       <c r="B34" s="11" t="s">
         <v>96</v>
       </c>
@@ -2250,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="17.25" spans="2:10">
+    <row r="35" ht="17.25" customHeight="1" spans="2:10">
       <c r="B35" s="11"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -2267,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="17.25" spans="2:10">
+    <row r="36" ht="17.25" customHeight="1" spans="2:10">
       <c r="B36" s="11"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -2284,7 +2326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" ht="17.25" spans="2:10">
+    <row r="37" ht="17.25" customHeight="1" spans="2:10">
       <c r="B37" s="11"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -2301,7 +2343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" ht="17.25" spans="2:10">
+    <row r="38" ht="17.25" customHeight="1" spans="2:10">
       <c r="B38" s="11"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -2318,7 +2360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" ht="17.25" spans="2:10">
+    <row r="39" ht="17.25" customHeight="1" spans="2:10">
       <c r="B39" s="11"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -2335,8 +2377,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" ht="17.25" spans="2:10">
-      <c r="B40" s="11" t="s">
+    <row r="40" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B40" s="12" t="s">
         <v>110</v>
       </c>
       <c r="C40" s="5" t="b">
@@ -2351,7 +2393,7 @@
       <c r="F40" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40" s="7"/>
       <c r="H40" s="6" t="s">
         <v>112</v>
       </c>
@@ -2362,120 +2404,242 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="17.25" spans="2:10">
-      <c r="B41" s="11"/>
+    <row r="41" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B41" s="13"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
-      <c r="G41" s="5"/>
+      <c r="G41" s="7"/>
       <c r="H41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="J41" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="17.25" spans="2:10">
-      <c r="B42" s="11"/>
+    <row r="42" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B42" s="14"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="9" t="s">
+      <c r="G42" s="7"/>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="J42" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="43" ht="17.25" spans="2:10">
-      <c r="B43" s="11"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="9" t="s">
+    <row r="43" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>118</v>
       </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="I43" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B44" s="13"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B45" s="14"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J45" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B46" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J46" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B47" s="11"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B48" s="11"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J48" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B49" s="11"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J49" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="44" ht="17.25" spans="2:10">
-      <c r="B44" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="13" t="b">
+    <row r="50" ht="17.25" spans="2:10">
+      <c r="B50" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D44" s="13" t="b">
+      <c r="D50" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E50" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J44" s="5">
+      <c r="F50" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" s="10"/>
+      <c r="H50" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J50" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="17.25" spans="2:10">
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="J45" s="5">
+    <row r="51" ht="17.25" spans="2:10">
+      <c r="B51" s="13"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J51" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="46" ht="17.25" spans="2:10">
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="J46" s="5">
+    <row r="52" ht="17.25" spans="2:10">
+      <c r="B52" s="14"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J52" s="5">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="61">
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
@@ -2485,8 +2649,10 @@
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C18"/>
@@ -2495,8 +2661,10 @@
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C29:C33"/>
     <mergeCell ref="C34:C39"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C50:C52"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D18"/>
@@ -2505,8 +2673,10 @@
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D33"/>
     <mergeCell ref="D34:D39"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="D50:D52"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E18"/>
@@ -2515,8 +2685,10 @@
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="E29:E33"/>
     <mergeCell ref="E34:E39"/>
-    <mergeCell ref="E40:E43"/>
-    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E50:E52"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F18"/>
@@ -2525,8 +2697,10 @@
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="F29:F33"/>
     <mergeCell ref="F34:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F50:F52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -321,12 +321,6 @@
   </si>
   <si>
     <t>幸运仪式增益类型</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>无增益</t>
   </si>
   <si>
     <t>MoreMeat</t>
@@ -1534,7 +1528,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1970,7 +1964,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:12">
+    <row r="19" ht="17.25" customHeight="1" spans="2:10">
       <c r="B19" s="6" t="s">
         <v>58</v>
       </c>
@@ -1997,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:12">
+    <row r="20" ht="17.25" customHeight="1" spans="2:10">
       <c r="B20" s="6"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -2014,7 +2008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:12">
+    <row r="21" ht="17.25" customHeight="1" spans="2:10">
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2031,7 +2025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:12">
+    <row r="22" ht="17.25" customHeight="1" spans="2:10">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -2048,7 +2042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:12">
+    <row r="23" ht="17.25" customHeight="1" spans="2:10">
       <c r="B23" s="6" t="s">
         <v>68</v>
       </c>
@@ -2075,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:12">
+    <row r="24" ht="17.25" customHeight="1" spans="2:10">
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2092,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:12">
+    <row r="25" ht="17.25" customHeight="1" spans="2:10">
       <c r="B25" s="6"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2109,7 +2103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:12">
+    <row r="26" ht="17.25" customHeight="1" spans="2:10">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2126,7 +2120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:12">
+    <row r="27" ht="17.25" customHeight="1" spans="2:10">
       <c r="B27" s="11" t="s">
         <v>78</v>
       </c>
@@ -2153,7 +2147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:12">
+    <row r="28" ht="17.25" customHeight="1" spans="2:10">
       <c r="B28" s="11"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2170,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:12">
+    <row r="29" ht="17.25" customHeight="1" spans="2:10">
       <c r="B29" s="11" t="s">
         <v>84</v>
       </c>
@@ -2197,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:12">
+    <row r="30" ht="17.25" customHeight="1" spans="2:10">
       <c r="B30" s="11"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2214,7 +2208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:12">
+    <row r="31" ht="17.25" customHeight="1" spans="2:10">
       <c r="B31" s="11"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2231,7 +2225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:12">
+    <row r="32" ht="17.25" customHeight="1" spans="2:10">
       <c r="B32" s="11"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2361,99 +2355,99 @@
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B39" s="11"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="10"/>
+      <c r="B39" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="7"/>
       <c r="H39" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J39" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B40" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>111</v>
-      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
       <c r="G40" s="7"/>
       <c r="H40" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="J40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B41" s="13"/>
+      <c r="B41" s="14"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
       <c r="G41" s="7"/>
       <c r="H41" s="6" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>114</v>
       </c>
       <c r="J41" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B42" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="14"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
+      <c r="E42" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="G42" s="7"/>
       <c r="H42" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J42" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
         <v>119</v>
@@ -2462,11 +2456,11 @@
         <v>120</v>
       </c>
       <c r="J43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="13"/>
+      <c r="B44" s="14"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2479,42 +2473,42 @@
         <v>122</v>
       </c>
       <c r="J44" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B45" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="14"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="7"/>
+      <c r="E45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="5"/>
       <c r="H45" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J45" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B46" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>126</v>
-      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
       <c r="G46" s="5"/>
       <c r="H46" s="6" t="s">
         <v>127</v>
@@ -2523,7 +2517,7 @@
         <v>128</v>
       </c>
       <c r="J46" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="2:10">
@@ -2533,14 +2527,14 @@
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="6" t="s">
+      <c r="H47" s="9" t="s">
         <v>129</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>130</v>
       </c>
       <c r="J47" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" ht="17.25" customHeight="1" spans="2:10">
@@ -2557,42 +2551,42 @@
         <v>132</v>
       </c>
       <c r="J48" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B49" s="11"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" spans="2:10">
+      <c r="B49" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G49" s="10"/>
       <c r="H49" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J49" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C50" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>136</v>
-      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="6"/>
       <c r="G50" s="10"/>
       <c r="H50" s="9" t="s">
         <v>137</v>
@@ -2601,14 +2595,14 @@
         <v>138</v>
       </c>
       <c r="J50" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="13"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
       <c r="F51" s="6"/>
       <c r="G51" s="10"/>
       <c r="H51" s="9" t="s">
@@ -2618,23 +2612,6 @@
         <v>140</v>
       </c>
       <c r="J51" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" ht="17.25" spans="2:10">
-      <c r="B52" s="14"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J52" s="5">
         <v>2</v>
       </c>
     </row>
@@ -2648,11 +2625,11 @@
     <mergeCell ref="B23:B26"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B49:B51"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C18"/>
@@ -2660,11 +2637,11 @@
     <mergeCell ref="C23:C26"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C51"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D18"/>
@@ -2672,11 +2649,11 @@
     <mergeCell ref="D23:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D33"/>
-    <mergeCell ref="D34:D39"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="D49:D51"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E18"/>
@@ -2684,11 +2661,11 @@
     <mergeCell ref="E23:E26"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="E29:E33"/>
-    <mergeCell ref="E34:E39"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="E49:E51"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F18"/>
@@ -2696,11 +2673,11 @@
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="F29:F33"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F43:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="F49:F51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="16785" windowHeight="9165"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="147">
   <si>
     <t>##var</t>
   </si>
@@ -396,6 +396,24 @@
   </si>
   <si>
     <t>高级礼包</t>
+  </si>
+  <si>
+    <t>特殊礼包</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyGiftCostType</t>
+  </si>
+  <si>
+    <t>礼包付费方式</t>
+  </si>
+  <si>
+    <t>ThreeKPCoin</t>
+  </si>
+  <si>
+    <t>Ad</t>
+  </si>
+  <si>
+    <t>广告</t>
   </si>
   <si>
     <t>HuntingConfig.Enum.EQuestType</t>
@@ -1154,7 +1172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1198,6 +1216,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1528,7 +1552,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1964,7 +1988,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="2:10">
+    <row r="19" ht="17.25" customHeight="1" spans="1:12">
       <c r="B19" s="6" t="s">
         <v>58</v>
       </c>
@@ -1991,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" spans="2:10">
+    <row r="20" ht="17.25" customHeight="1" spans="1:12">
       <c r="B20" s="6"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -2008,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1" spans="2:10">
+    <row r="21" ht="17.25" customHeight="1" spans="1:12">
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2025,7 +2049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1" spans="2:10">
+    <row r="22" ht="17.25" customHeight="1" spans="1:12">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -2042,7 +2066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="2:10">
+    <row r="23" ht="17.25" customHeight="1" spans="1:12">
       <c r="B23" s="6" t="s">
         <v>68</v>
       </c>
@@ -2069,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1" spans="2:10">
+    <row r="24" ht="17.25" customHeight="1" spans="1:12">
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2086,7 +2110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1" spans="2:10">
+    <row r="25" ht="17.25" customHeight="1" spans="1:12">
       <c r="B25" s="6"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2103,7 +2127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1" spans="2:10">
+    <row r="26" ht="17.25" customHeight="1" spans="1:12">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2120,7 +2144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1" spans="2:10">
+    <row r="27" ht="17.25" customHeight="1" spans="1:12">
       <c r="B27" s="11" t="s">
         <v>78</v>
       </c>
@@ -2147,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" spans="2:10">
+    <row r="28" ht="17.25" customHeight="1" spans="1:12">
       <c r="B28" s="11"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2164,7 +2188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" spans="2:10">
+    <row r="29" ht="17.25" customHeight="1" spans="1:12">
       <c r="B29" s="11" t="s">
         <v>84</v>
       </c>
@@ -2191,7 +2215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" spans="2:10">
+    <row r="30" ht="17.25" customHeight="1" spans="1:12">
       <c r="B30" s="11"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2208,7 +2232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" spans="2:10">
+    <row r="31" ht="17.25" customHeight="1" spans="1:12">
       <c r="B31" s="11"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2225,7 +2249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1" spans="2:10">
+    <row r="32" ht="17.25" customHeight="1" spans="1:12">
       <c r="B32" s="11"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2416,16 +2440,16 @@
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="5" t="b">
+      <c r="C42" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="D42" s="5" t="b">
+      <c r="D42" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="6" t="s">
@@ -2443,10 +2467,10 @@
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="13"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
       <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
@@ -2460,10 +2484,10 @@
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="14"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
       <c r="F44" s="6"/>
       <c r="G44" s="7"/>
       <c r="H44" s="6" t="s">
@@ -2477,47 +2501,47 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="15"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="5" t="b">
+      <c r="J45" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B46" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D45" s="5" t="b">
+      <c r="D46" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="G46" s="7"/>
+      <c r="H46" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J45" s="5">
+      <c r="I46" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J46" s="5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B46" s="11"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J46" s="5">
-        <v>1</v>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="2:10">
@@ -2526,97 +2550,158 @@
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="9" t="s">
+      <c r="G47" s="7"/>
+      <c r="H47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J47" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B48" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="C48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J47" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B48" s="11"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>132</v>
       </c>
       <c r="J48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" spans="2:10">
+      <c r="B49" s="11"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" spans="2:10">
+      <c r="B50" s="11"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" spans="2:10">
+      <c r="B51" s="11"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J51" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="49" ht="17.25" spans="2:10">
-      <c r="B49" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C49" s="15" t="b">
+    <row r="52" ht="17.25" spans="2:10">
+      <c r="B52" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="D49" s="15" t="b">
+      <c r="D52" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E52" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="J49" s="5">
+      <c r="F52" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="H52" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J52" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="13"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J50" s="5">
+    <row r="53" ht="17.25" spans="2:10">
+      <c r="B53" s="13"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J53" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="14"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J51" s="5">
+    <row r="54" ht="17.25" spans="2:10">
+      <c r="B54" s="14"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J54" s="5">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="66">
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
@@ -2627,9 +2712,10 @@
     <mergeCell ref="B29:B33"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B52:B54"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C18"/>
@@ -2639,9 +2725,10 @@
     <mergeCell ref="C29:C33"/>
     <mergeCell ref="C34:C38"/>
     <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="C52:C54"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D18"/>
@@ -2651,9 +2738,10 @@
     <mergeCell ref="D29:D33"/>
     <mergeCell ref="D34:D38"/>
     <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="D49:D51"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D51"/>
+    <mergeCell ref="D52:D54"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E18"/>
@@ -2663,9 +2751,10 @@
     <mergeCell ref="E29:E33"/>
     <mergeCell ref="E34:E38"/>
     <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E45:E48"/>
-    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E52:E54"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F18"/>
@@ -2675,9 +2764,10 @@
     <mergeCell ref="F29:F33"/>
     <mergeCell ref="F34:F38"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="F45:F48"/>
-    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="F52:F54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16785" windowHeight="9165"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -167,7 +167,7 @@
     <t>新疆大草原</t>
   </si>
   <si>
-    <t>Mountain</t>
+    <t>Hidden</t>
   </si>
   <si>
     <t>远古雪山</t>
@@ -1172,7 +1172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1216,12 +1216,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2440,16 +2434,16 @@
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="16" t="b">
+      <c r="C42" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D42" s="16" t="b">
+      <c r="D42" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="6" t="s">
@@ -2467,10 +2461,10 @@
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="15"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
       <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
@@ -2484,10 +2478,10 @@
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="15"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
       <c r="F44" s="6"/>
       <c r="G44" s="7"/>
       <c r="H44" s="6" t="s">
@@ -2501,10 +2495,10 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="6"/>
       <c r="G45" s="7"/>
       <c r="H45" s="6" t="s">
@@ -2643,13 +2637,13 @@
       <c r="B52" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="17" t="b">
+      <c r="C52" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="D52" s="17" t="b">
+      <c r="D52" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="15" t="s">
         <v>22</v>
       </c>
       <c r="F52" s="6" t="s">
@@ -2668,9 +2662,9 @@
     </row>
     <row r="53" ht="17.25" spans="2:10">
       <c r="B53" s="13"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
       <c r="F53" s="6"/>
       <c r="G53" s="10"/>
       <c r="H53" s="9" t="s">
@@ -2685,9 +2679,9 @@
     </row>
     <row r="54" ht="17.25" spans="2:10">
       <c r="B54" s="14"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="6"/>
       <c r="G54" s="10"/>
       <c r="H54" s="9" t="s">

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>特殊体型</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>Boss体型</t>
   </si>
   <si>
     <t>HuntingConfig.Enum.EDropType</t>
@@ -1172,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1198,6 +1204,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1894,22 +1906,22 @@
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:12">
       <c r="A15" s="8"/>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="5" t="b">
+      <c r="C15" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="D15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="7"/>
       <c r="H15" s="6" t="s">
         <v>50</v>
       </c>
@@ -1924,12 +1936,12 @@
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:12">
       <c r="A16" s="8"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="7"/>
       <c r="H16" s="6" t="s">
         <v>52</v>
       </c>
@@ -1944,12 +1956,12 @@
     </row>
     <row r="17" ht="17.25" customHeight="1" spans="1:12">
       <c r="A17" s="8"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="6" t="s">
         <v>54</v>
       </c>
@@ -1964,12 +1976,12 @@
     </row>
     <row r="18" ht="17.25" customHeight="1" spans="1:12">
       <c r="A18" s="8"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="7"/>
       <c r="H18" s="6" t="s">
         <v>56</v>
       </c>
@@ -1982,117 +1994,117 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B19" s="6" t="s">
+    <row r="19" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="5" t="b">
+      <c r="I19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="b">
+      <c r="D20" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B20" s="6"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="11" t="s">
         <v>62</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>63</v>
       </c>
       <c r="J20" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="17.25" customHeight="1" spans="2:10">
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="11" t="s">
         <v>64</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="J21" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1" spans="2:10">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9" t="s">
+      <c r="G22" s="5"/>
+      <c r="H22" s="11" t="s">
         <v>66</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>67</v>
       </c>
       <c r="J22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B23" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="5" t="b">
+    <row r="24" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B24" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="b">
+      <c r="D24" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B24" s="6"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
       <c r="G24" s="5"/>
       <c r="H24" s="6" t="s">
         <v>72</v>
@@ -2101,10 +2113,10 @@
         <v>73</v>
       </c>
       <c r="J24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1" spans="2:10">
       <c r="B25" s="6"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2118,10 +2130,10 @@
         <v>75</v>
       </c>
       <c r="J25" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1" spans="2:10">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2135,42 +2147,42 @@
         <v>77</v>
       </c>
       <c r="J26" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B27" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="5"/>
       <c r="H27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B28" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="C28" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B28" s="11"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
       <c r="G28" s="5"/>
       <c r="H28" s="6" t="s">
         <v>82</v>
@@ -2179,42 +2191,42 @@
         <v>83</v>
       </c>
       <c r="J28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B29" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>85</v>
-      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B29" s="13"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
       <c r="G29" s="5"/>
       <c r="H29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B30" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="C30" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B30" s="11"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
       <c r="G30" s="5"/>
       <c r="H30" s="6" t="s">
         <v>88</v>
@@ -2223,11 +2235,11 @@
         <v>89</v>
       </c>
       <c r="J30" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B31" s="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B31" s="13"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -2240,11 +2252,11 @@
         <v>91</v>
       </c>
       <c r="J31" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B32" s="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B32" s="13"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -2257,11 +2269,11 @@
         <v>93</v>
       </c>
       <c r="J32" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B33" s="11"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -2274,42 +2286,42 @@
         <v>95</v>
       </c>
       <c r="J33" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B34" s="13"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J34" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B34" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" s="5" t="b">
+    <row r="35" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B35" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D34" s="5" t="b">
+      <c r="D35" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J34" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B35" s="11"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
       <c r="G35" s="7"/>
       <c r="H35" s="6" t="s">
         <v>100</v>
@@ -2318,11 +2330,11 @@
         <v>101</v>
       </c>
       <c r="J35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B36" s="11"/>
+      <c r="B36" s="13"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2335,11 +2347,11 @@
         <v>103</v>
       </c>
       <c r="J36" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B37" s="11"/>
+      <c r="B37" s="13"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2352,11 +2364,11 @@
         <v>105</v>
       </c>
       <c r="J37" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B38" s="11"/>
+      <c r="B38" s="13"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2369,103 +2381,103 @@
         <v>107</v>
       </c>
       <c r="J38" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B39" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>109</v>
-      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
       <c r="G39" s="7"/>
       <c r="H39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J39" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B40" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="C40" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J39" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B40" s="13"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
       <c r="G40" s="7"/>
       <c r="H40" s="6" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B41" s="14"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
       <c r="G41" s="7"/>
       <c r="H41" s="6" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>114</v>
       </c>
       <c r="J41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>116</v>
-      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
       <c r="G42" s="7"/>
       <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J42" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B43" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="C43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="J42" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="11"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
         <v>119</v>
@@ -2474,11 +2486,11 @@
         <v>120</v>
       </c>
       <c r="J43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="11"/>
+      <c r="B44" s="13"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -2491,103 +2503,103 @@
         <v>122</v>
       </c>
       <c r="J44" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="11"/>
+      <c r="B45" s="13"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
       <c r="G45" s="7"/>
       <c r="H45" s="6" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J45" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B46" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>125</v>
-      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
       <c r="G46" s="7"/>
       <c r="H46" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J46" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B47" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J46" s="5">
+      <c r="C47" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B47" s="11"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
+      <c r="D47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="G47" s="7"/>
       <c r="H47" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="J47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B48" s="13"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J48" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B48" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C48" s="5" t="b">
+    <row r="49" ht="17.25" spans="2:10">
+      <c r="B49" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D48" s="5" t="b">
+      <c r="D49" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="I48" s="6" t="s">
+      <c r="F49" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J48" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="17.25" spans="2:10">
-      <c r="B49" s="11"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6"/>
       <c r="G49" s="5"/>
       <c r="H49" s="6" t="s">
         <v>133</v>
@@ -2596,101 +2608,118 @@
         <v>134</v>
       </c>
       <c r="J49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="11"/>
+      <c r="B50" s="13"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="6"/>
       <c r="G50" s="5"/>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="6" t="s">
         <v>135</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>136</v>
       </c>
       <c r="J50" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="11"/>
+      <c r="B51" s="13"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="6"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="11" t="s">
         <v>137</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>138</v>
       </c>
       <c r="J51" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" ht="17.25" spans="2:10">
+      <c r="B52" s="13"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J52" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="52" ht="17.25" spans="2:10">
-      <c r="B52" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" s="15" t="b">
+    <row r="53" ht="17.25" spans="2:10">
+      <c r="B53" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="D52" s="15" t="b">
+      <c r="D53" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E53" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G52" s="10"/>
-      <c r="H52" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I52" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="J52" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="17.25" spans="2:10">
-      <c r="B53" s="13"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="9" t="s">
+      <c r="G53" s="12"/>
+      <c r="H53" s="11" t="s">
         <v>143</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>144</v>
       </c>
       <c r="J53" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" ht="17.25" spans="2:10">
-      <c r="B54" s="14"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="6"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="9" t="s">
+      <c r="G54" s="12"/>
+      <c r="H54" s="11" t="s">
         <v>145</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>146</v>
       </c>
       <c r="J54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" spans="2:10">
+      <c r="B55" s="16"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J55" s="5">
         <v>2</v>
       </c>
     </row>
@@ -2699,69 +2728,69 @@
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="B53:B55"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C34"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="C53:C55"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D51"/>
-    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D34"/>
+    <mergeCell ref="D35:D39"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="D53:D55"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="E24:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E34"/>
+    <mergeCell ref="E35:E39"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="E53:E55"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
-    <mergeCell ref="F15:F18"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="F48:F51"/>
-    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="F35:F39"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="F53:F55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -173,7 +173,7 @@
     <t>远古雪山</t>
   </si>
   <si>
-    <t>HuntingConfig.Enum.EVolumeType</t>
+    <t>HuntingConfig.Enum.ESpecieType</t>
   </si>
   <si>
     <t>物种体型类型</t>
@@ -182,228 +182,231 @@
     <t>Small</t>
   </si>
   <si>
-    <t>小体型</t>
+    <t>小型动物</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>中体型</t>
+    <t>中型动物</t>
   </si>
   <si>
     <t>Large</t>
   </si>
   <si>
-    <t>大体型</t>
+    <t>大型动物</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+  </si>
+  <si>
+    <t>弹药动物</t>
+  </si>
+  <si>
+    <t>ThreeKPCoin</t>
+  </si>
+  <si>
+    <t>3KP金币动物</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>Boss动物</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.EDropType</t>
+  </si>
+  <si>
+    <t>物种掉落物类型</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>肉</t>
+  </si>
+  <si>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>3KP金币</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>丰收能量</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.EBulletType</t>
+  </si>
+  <si>
+    <t>子弹类型</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通子弹</t>
+  </si>
+  <si>
+    <t>Explosive</t>
+  </si>
+  <si>
+    <t>爆炸子弹</t>
+  </si>
+  <si>
+    <t>HighDamage</t>
+  </si>
+  <si>
+    <t>高伤子弹</t>
+  </si>
+  <si>
+    <t>HighSpeed</t>
+  </si>
+  <si>
+    <t>高速子弹</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.EBulletDamageRangeType</t>
+  </si>
+  <si>
+    <t>子弹伤害范围类型</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>单体伤害</t>
+  </si>
+  <si>
+    <t>AOE</t>
+  </si>
+  <si>
+    <t>范围伤害</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ESkillType</t>
+  </si>
+  <si>
+    <t>技能类型</t>
+  </si>
+  <si>
+    <t>_3KPSkill</t>
+  </si>
+  <si>
+    <t>色块人技能</t>
+  </si>
+  <si>
+    <t>ZiWeiSkill</t>
+  </si>
+  <si>
+    <t>紫薇技能</t>
+  </si>
+  <si>
+    <t>DaMeiLiSkill</t>
+  </si>
+  <si>
+    <t>大美丽技能</t>
+  </si>
+  <si>
+    <t>JinZhuangYuanSkill</t>
+  </si>
+  <si>
+    <t>金状元技能</t>
+  </si>
+  <si>
+    <t>YaKeDongSkill</t>
+  </si>
+  <si>
+    <t>亚克东技能</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyBuffType</t>
+  </si>
+  <si>
+    <t>幸运仪式增益类型</t>
+  </si>
+  <si>
+    <t>MoreMeat</t>
+  </si>
+  <si>
+    <t>更多大肉</t>
+  </si>
+  <si>
+    <t>StartSpecialBullet</t>
+  </si>
+  <si>
+    <t>开局特殊子弹</t>
+  </si>
+  <si>
+    <t>StartEnergy</t>
+  </si>
+  <si>
+    <t>开局丰收能量</t>
+  </si>
+  <si>
+    <t>DamageBoost</t>
+  </si>
+  <si>
+    <t>伤害提升</t>
+  </si>
+  <si>
+    <t>HighTierSpawn</t>
+  </si>
+  <si>
+    <t>高阶派发</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyBuffStrengthType</t>
+  </si>
+  <si>
+    <t>幸运仪式增益强度类型</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>弱档</t>
+  </si>
+  <si>
+    <t>中档</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>强档</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.ELuckyGiftType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幸运仪式礼包类型 </t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>初级礼包</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>中级礼包</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>高级礼包</t>
   </si>
   <si>
     <t>Special</t>
   </si>
   <si>
-    <t>特殊体型</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>Boss体型</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.EDropType</t>
-  </si>
-  <si>
-    <t>物种掉落物类型</t>
-  </si>
-  <si>
-    <t>Meat</t>
-  </si>
-  <si>
-    <t>回血肉</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>子弹</t>
-  </si>
-  <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>3KP金币</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>丰收能量</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.EBulletType</t>
-  </si>
-  <si>
-    <t>子弹类型</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>普通子弹</t>
-  </si>
-  <si>
-    <t>Explosive</t>
-  </si>
-  <si>
-    <t>爆炸子弹</t>
-  </si>
-  <si>
-    <t>HighDamage</t>
-  </si>
-  <si>
-    <t>高伤子弹</t>
-  </si>
-  <si>
-    <t>HighSpeed</t>
-  </si>
-  <si>
-    <t>高速子弹</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.EBulletDamageRangeType</t>
-  </si>
-  <si>
-    <t>子弹伤害范围类型</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>单体伤害</t>
-  </si>
-  <si>
-    <t>AOE</t>
-  </si>
-  <si>
-    <t>范围伤害</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.ESkillType</t>
-  </si>
-  <si>
-    <t>技能类型</t>
-  </si>
-  <si>
-    <t>_3KPSkill</t>
-  </si>
-  <si>
-    <t>色块人技能</t>
-  </si>
-  <si>
-    <t>ZiWeiSkill</t>
-  </si>
-  <si>
-    <t>紫薇技能</t>
-  </si>
-  <si>
-    <t>DaMeiLiSkill</t>
-  </si>
-  <si>
-    <t>大美丽技能</t>
-  </si>
-  <si>
-    <t>JinZhuangYuanSkill</t>
-  </si>
-  <si>
-    <t>金状元技能</t>
-  </si>
-  <si>
-    <t>YaKeDongSkill</t>
-  </si>
-  <si>
-    <t>亚克东技能</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.ELuckyBuffType</t>
-  </si>
-  <si>
-    <t>幸运仪式增益类型</t>
-  </si>
-  <si>
-    <t>MoreMeat</t>
-  </si>
-  <si>
-    <t>更多大肉</t>
-  </si>
-  <si>
-    <t>StartSpecialBullet</t>
-  </si>
-  <si>
-    <t>开局特殊子弹</t>
-  </si>
-  <si>
-    <t>StartEnergy</t>
-  </si>
-  <si>
-    <t>开局丰收能量</t>
-  </si>
-  <si>
-    <t>DamageBoost</t>
-  </si>
-  <si>
-    <t>伤害提升</t>
-  </si>
-  <si>
-    <t>HighTierSpawn</t>
-  </si>
-  <si>
-    <t>高阶派发</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.ELuckyBuffStrengthType</t>
-  </si>
-  <si>
-    <t>幸运仪式增益强度类型</t>
-  </si>
-  <si>
-    <t>Weak</t>
-  </si>
-  <si>
-    <t>弱档</t>
-  </si>
-  <si>
-    <t>中档</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>强档</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.ELuckyGiftType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">幸运仪式礼包类型 </t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>初级礼包</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>中级礼包</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>高级礼包</t>
-  </si>
-  <si>
     <t>特殊礼包</t>
   </si>
   <si>
@@ -411,9 +414,6 @@
   </si>
   <si>
     <t>礼包付费方式</t>
-  </si>
-  <si>
-    <t>ThreeKPCoin</t>
   </si>
   <si>
     <t>Ad</t>
@@ -1178,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1206,10 +1206,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,7 +1576,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -1936,11 +1954,11 @@
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:12">
       <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="7"/>
       <c r="H16" s="6" t="s">
         <v>52</v>
@@ -1956,11 +1974,11 @@
     </row>
     <row r="17" ht="17.25" customHeight="1" spans="1:12">
       <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="7"/>
       <c r="H17" s="6" t="s">
         <v>54</v>
@@ -1976,11 +1994,11 @@
     </row>
     <row r="18" ht="17.25" customHeight="1" spans="1:12">
       <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="7"/>
       <c r="H18" s="6" t="s">
         <v>56</v>
@@ -1994,12 +2012,12 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="9"/>
+    <row r="19" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="7"/>
       <c r="H19" s="6" t="s">
         <v>58</v>
@@ -2011,129 +2029,129 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B20" s="6" t="s">
+    <row r="20" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="5" t="b">
+      <c r="I20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="5" t="b">
+      <c r="D21" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B21" s="6"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="17" t="s">
         <v>64</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="J21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="17.25" customHeight="1" spans="2:10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1" spans="1:12">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="J22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" ht="17.25" customHeight="1" spans="2:10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1" spans="1:12">
       <c r="B23" s="6"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="11" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J24" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B24" s="6" t="s">
+    <row r="25" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="5" t="b">
+      <c r="C25" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D24" s="5" t="b">
+      <c r="D25" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B25" s="6"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
       <c r="G25" s="5"/>
       <c r="H25" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="17.25" customHeight="1" spans="2:10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1" spans="1:12">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2141,16 +2159,16 @@
       <c r="F26" s="6"/>
       <c r="G26" s="5"/>
       <c r="H26" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J26" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="2:10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="1:12">
       <c r="B27" s="6"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -2158,568 +2176,585 @@
       <c r="F27" s="6"/>
       <c r="G27" s="5"/>
       <c r="H27" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J27" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B28" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
       <c r="G28" s="5"/>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J28" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B29" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B29" s="13"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
+      <c r="D29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J29" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B30" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>87</v>
-      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B30" s="19"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
       <c r="G30" s="5"/>
       <c r="H30" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B31" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B31" s="13"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
+      <c r="D31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B32" s="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="1:12">
+      <c r="B32" s="19"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="6"/>
       <c r="G32" s="5"/>
       <c r="H32" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B33" s="13"/>
+      <c r="B33" s="19"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
       <c r="G33" s="5"/>
       <c r="H33" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J33" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B34" s="13"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
       <c r="G34" s="5"/>
       <c r="H34" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B35" s="19"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J35" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B35" s="13" t="s">
+    <row r="36" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B36" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="5" t="b">
+      <c r="C36" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="5" t="b">
+      <c r="D36" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J35" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B36" s="13"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
       <c r="G36" s="7"/>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B37" s="13"/>
+      <c r="B37" s="19"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="6"/>
       <c r="G37" s="7"/>
       <c r="H37" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J37" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B38" s="13"/>
+      <c r="B38" s="19"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
       <c r="G38" s="7"/>
       <c r="H38" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J38" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B39" s="13"/>
+      <c r="B39" s="19"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="6"/>
       <c r="G39" s="7"/>
       <c r="H39" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J39" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B40" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>111</v>
-      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
       <c r="G40" s="7"/>
       <c r="H40" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J40" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B41" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B41" s="15"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
+      <c r="D41" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="G41" s="7"/>
       <c r="H41" s="6" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J41" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="16"/>
+      <c r="B42" s="21"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="7"/>
       <c r="H42" s="6" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J42" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J43" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B44" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="13"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
+      <c r="D44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="G44" s="7"/>
       <c r="H44" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="13"/>
+      <c r="B45" s="19"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
       <c r="G45" s="7"/>
       <c r="H45" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J45" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B46" s="13"/>
+      <c r="B46" s="19"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
       <c r="G46" s="7"/>
       <c r="H46" s="6" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J46" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B47" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
       <c r="G47" s="7"/>
       <c r="H47" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B48" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I47" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B48" s="13"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
       <c r="G48" s="7"/>
       <c r="H48" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B49" s="19"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I49" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J49" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="49" ht="17.25" spans="2:10">
-      <c r="B49" s="13" t="s">
+    <row r="50" ht="17.25" spans="2:10">
+      <c r="B50" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="5" t="b">
+      <c r="C50" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D49" s="5" t="b">
+      <c r="D50" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F50" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="J49" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="13"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6"/>
       <c r="G50" s="5"/>
       <c r="H50" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="13"/>
+      <c r="B51" s="19"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="6"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="11" t="s">
-        <v>137</v>
+      <c r="H51" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J51" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" ht="17.25" spans="2:10">
-      <c r="B52" s="13"/>
+      <c r="B52" s="19"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="6"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J52" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" ht="17.25" spans="2:10">
+      <c r="B53" s="19"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I53" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J53" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="53" ht="17.25" spans="2:10">
-      <c r="B53" s="14" t="s">
+    <row r="54" ht="17.25" spans="2:10">
+      <c r="B54" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="17" t="b">
+      <c r="C54" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D53" s="17" t="b">
+      <c r="D54" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E54" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G53" s="12"/>
-      <c r="H53" s="11" t="s">
+      <c r="G54" s="18"/>
+      <c r="H54" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I54" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J54" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="17.25" spans="2:10">
-      <c r="B54" s="15"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="11" t="s">
+    <row r="55" ht="17.25" spans="2:10">
+      <c r="B55" s="21"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I55" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J55" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="55" ht="17.25" spans="2:10">
-      <c r="B55" s="16"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="11" t="s">
+    <row r="56" ht="17.25" spans="2:10">
+      <c r="B56" s="22"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I56" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J56" s="5">
         <v>2</v>
       </c>
     </row>
@@ -2728,69 +2763,69 @@
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B54:B56"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
-    <mergeCell ref="C15:C19"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C35"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="C54:C56"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D34"/>
-    <mergeCell ref="D35:D39"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D35"/>
+    <mergeCell ref="D36:D40"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="D54:D56"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
-    <mergeCell ref="E15:E19"/>
-    <mergeCell ref="E20:E23"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E34"/>
-    <mergeCell ref="E35:E39"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E43:E46"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="E15:E20"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="E54:E56"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
-    <mergeCell ref="F15:F19"/>
-    <mergeCell ref="F20:F23"/>
-    <mergeCell ref="F24:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="F35:F39"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="F36:F40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F54:F56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="161">
   <si>
     <t>##var</t>
   </si>
@@ -474,6 +474,42 @@
   </si>
   <si>
     <t>智能诱捕陷阱</t>
+  </si>
+  <si>
+    <t>HuntingConfig.Enum.EBossType</t>
+  </si>
+  <si>
+    <t>Boss类型</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>BeiJiXiong</t>
+  </si>
+  <si>
+    <t>北极熊</t>
+  </si>
+  <si>
+    <t>MengMaXiang</t>
+  </si>
+  <si>
+    <t>猛犸象</t>
+  </si>
+  <si>
+    <t>XueXingXing</t>
+  </si>
+  <si>
+    <t>雪猩猩</t>
+  </si>
+  <si>
+    <t>SanJiaoLong</t>
+  </si>
+  <si>
+    <t>三角龙</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1224,15 +1260,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1248,13 +1278,31 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1576,7 +1624,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -2035,8 +2083,8 @@
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16" t="s">
+      <c r="G20" s="7"/>
+      <c r="H20" s="15" t="s">
         <v>60</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -2063,7 +2111,7 @@
         <v>63</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="15" t="s">
         <v>64</v>
       </c>
       <c r="I21" s="6" t="s">
@@ -2080,7 +2128,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="15" t="s">
         <v>56</v>
       </c>
       <c r="I22" s="6" t="s">
@@ -2097,7 +2145,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="15" t="s">
         <v>58</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -2113,8 +2161,8 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="17" t="s">
+      <c r="G24" s="16"/>
+      <c r="H24" s="15" t="s">
         <v>68</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -2203,7 +2251,7 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="17" t="s">
         <v>80</v>
       </c>
       <c r="C29" s="5" t="b">
@@ -2230,7 +2278,7 @@
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B30" s="19"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -2247,7 +2295,7 @@
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="17" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="5" t="b">
@@ -2274,7 +2322,7 @@
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1" spans="1:12">
-      <c r="B32" s="19"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -2291,7 +2339,7 @@
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B33" s="19"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -2308,7 +2356,7 @@
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B34" s="19"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -2325,7 +2373,7 @@
       </c>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B35" s="19"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -2342,7 +2390,7 @@
       </c>
     </row>
     <row r="36" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="17" t="s">
         <v>98</v>
       </c>
       <c r="C36" s="5" t="b">
@@ -2369,7 +2417,7 @@
       </c>
     </row>
     <row r="37" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B37" s="19"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2386,7 +2434,7 @@
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B38" s="19"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2403,7 +2451,7 @@
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B39" s="19"/>
+      <c r="B39" s="17"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2420,7 +2468,7 @@
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B40" s="19"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2437,7 +2485,7 @@
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="18" t="s">
         <v>110</v>
       </c>
       <c r="C41" s="5" t="b">
@@ -2464,7 +2512,7 @@
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="21"/>
+      <c r="B42" s="19"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -2481,7 +2529,7 @@
       </c>
     </row>
     <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="22"/>
+      <c r="B43" s="20"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -2498,7 +2546,7 @@
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="17" t="s">
         <v>117</v>
       </c>
       <c r="C44" s="5" t="b">
@@ -2525,7 +2573,7 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B45" s="19"/>
+      <c r="B45" s="17"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2542,7 +2590,7 @@
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B46" s="19"/>
+      <c r="B46" s="17"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2559,7 +2607,7 @@
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B47" s="19"/>
+      <c r="B47" s="17"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2576,7 +2624,7 @@
       </c>
     </row>
     <row r="48" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="17" t="s">
         <v>127</v>
       </c>
       <c r="C48" s="5" t="b">
@@ -2603,7 +2651,7 @@
       </c>
     </row>
     <row r="49" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B49" s="19"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2620,7 +2668,7 @@
       </c>
     </row>
     <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>131</v>
       </c>
       <c r="C50" s="5" t="b">
@@ -2647,7 +2695,7 @@
       </c>
     </row>
     <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="19"/>
+      <c r="B51" s="17"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2664,13 +2712,13 @@
       </c>
     </row>
     <row r="52" ht="17.25" spans="2:10">
-      <c r="B52" s="19"/>
+      <c r="B52" s="17"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="6"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="17" t="s">
+      <c r="H52" s="15" t="s">
         <v>137</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -2681,13 +2729,13 @@
       </c>
     </row>
     <row r="53" ht="17.25" spans="2:10">
-      <c r="B53" s="19"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="6"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="15" t="s">
         <v>139</v>
       </c>
       <c r="I53" s="6" t="s">
@@ -2698,23 +2746,23 @@
       </c>
     </row>
     <row r="54" ht="17.25" spans="2:10">
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="23" t="b">
+      <c r="C54" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D54" s="23" t="b">
+      <c r="D54" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G54" s="18"/>
-      <c r="H54" s="17" t="s">
+      <c r="G54" s="16"/>
+      <c r="H54" s="15" t="s">
         <v>143</v>
       </c>
       <c r="I54" s="6" t="s">
@@ -2725,13 +2773,13 @@
       </c>
     </row>
     <row r="55" ht="17.25" spans="2:10">
-      <c r="B55" s="21"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
       <c r="F55" s="6"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="17" t="s">
+      <c r="G55" s="16"/>
+      <c r="H55" s="15" t="s">
         <v>145</v>
       </c>
       <c r="I55" s="6" t="s">
@@ -2742,13 +2790,13 @@
       </c>
     </row>
     <row r="56" ht="17.25" spans="2:10">
-      <c r="B56" s="22"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
       <c r="F56" s="6"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="17" t="s">
+      <c r="G56" s="16"/>
+      <c r="H56" s="15" t="s">
         <v>147</v>
       </c>
       <c r="I56" s="6" t="s">
@@ -2758,8 +2806,103 @@
         <v>2</v>
       </c>
     </row>
+    <row r="57" ht="17.25" spans="2:10">
+      <c r="B57" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="24"/>
+      <c r="H57" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" spans="2:10">
+      <c r="B58" s="21"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J58" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" spans="2:10">
+      <c r="B59" s="21"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" spans="2:10">
+      <c r="B60" s="21"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J60" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" spans="2:10">
+      <c r="B61" s="27"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J61" s="5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="71">
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
@@ -2774,6 +2917,7 @@
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B61"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C20"/>
@@ -2787,6 +2931,7 @@
     <mergeCell ref="C48:C49"/>
     <mergeCell ref="C50:C53"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="C57:C61"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D20"/>
@@ -2800,6 +2945,7 @@
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="D50:D53"/>
     <mergeCell ref="D54:D56"/>
+    <mergeCell ref="D57:D61"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E20"/>
@@ -2813,6 +2959,7 @@
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="E50:E53"/>
     <mergeCell ref="E54:E56"/>
+    <mergeCell ref="E57:E61"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F20"/>
@@ -2826,6 +2973,7 @@
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="F50:F53"/>
     <mergeCell ref="F54:F56"/>
+    <mergeCell ref="F57:F61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1214,7 +1214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1278,32 +1278,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2807,22 +2783,22 @@
       </c>
     </row>
     <row r="57" ht="17.25" spans="2:10">
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C57" s="22" t="b">
+      <c r="C57" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D57" s="22" t="b">
+      <c r="D57" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F57" s="23" t="s">
+      <c r="F57" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G57" s="24"/>
+      <c r="G57" s="21"/>
       <c r="H57" s="15" t="s">
         <v>151</v>
       </c>
@@ -2834,12 +2810,12 @@
       </c>
     </row>
     <row r="58" ht="17.25" spans="2:10">
-      <c r="B58" s="21"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="26"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="21"/>
       <c r="H58" s="15" t="s">
         <v>153</v>
       </c>
@@ -2851,12 +2827,12 @@
       </c>
     </row>
     <row r="59" ht="17.25" spans="2:10">
-      <c r="B59" s="21"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="26"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="21"/>
       <c r="H59" s="15" t="s">
         <v>155</v>
       </c>
@@ -2868,12 +2844,12 @@
       </c>
     </row>
     <row r="60" ht="17.25" spans="2:10">
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="26"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="21"/>
       <c r="H60" s="15" t="s">
         <v>157</v>
       </c>
@@ -2885,12 +2861,12 @@
       </c>
     </row>
     <row r="61" ht="17.25" spans="2:10">
-      <c r="B61" s="27"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="26"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="21"/>
       <c r="H61" s="15" t="s">
         <v>159</v>
       </c>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="159">
   <si>
     <t>##var</t>
   </si>
@@ -428,28 +428,22 @@
     <t>任务类型</t>
   </si>
   <si>
-    <t>KillLargeAnimal</t>
-  </si>
-  <si>
-    <t>击杀大型动物</t>
-  </si>
-  <si>
-    <t>CollectMeat</t>
-  </si>
-  <si>
-    <t>收集回血肉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UsePaidItem </t>
-  </si>
-  <si>
-    <t>使用付费道具</t>
-  </si>
-  <si>
-    <t>Settle</t>
-  </si>
-  <si>
-    <t>进行结算</t>
+    <t>Hunting</t>
+  </si>
+  <si>
+    <t>狩猎</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>收集</t>
+  </si>
+  <si>
+    <t>Consume</t>
+  </si>
+  <si>
+    <t>消耗</t>
   </si>
   <si>
     <t>HuntingConfig.Enum.EPropType</t>
@@ -1214,7 +1208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1276,6 +1270,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -1600,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -2036,7 +2033,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:12">
+    <row r="19" ht="17.25" customHeight="1" spans="2:10">
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2053,7 +2050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:12">
+    <row r="20" ht="17.25" customHeight="1" spans="2:10">
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -2070,7 +2067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:12">
+    <row r="21" ht="17.25" customHeight="1" spans="2:10">
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -2097,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:12">
+    <row r="22" ht="17.25" customHeight="1" spans="2:10">
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -2114,7 +2111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:12">
+    <row r="23" ht="17.25" customHeight="1" spans="2:10">
       <c r="B23" s="6"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -2131,7 +2128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:12">
+    <row r="24" ht="17.25" customHeight="1" spans="2:10">
       <c r="B24" s="6"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2148,7 +2145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:12">
+    <row r="25" ht="17.25" customHeight="1" spans="2:10">
       <c r="B25" s="6" t="s">
         <v>70</v>
       </c>
@@ -2175,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:12">
+    <row r="26" ht="17.25" customHeight="1" spans="2:10">
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2192,7 +2189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:12">
+    <row r="27" ht="17.25" customHeight="1" spans="2:10">
       <c r="B27" s="6"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -2209,7 +2206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:12">
+    <row r="28" ht="17.25" customHeight="1" spans="2:10">
       <c r="B28" s="6"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2226,7 +2223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:12">
+    <row r="29" ht="17.25" customHeight="1" spans="2:10">
       <c r="B29" s="17" t="s">
         <v>80</v>
       </c>
@@ -2253,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:12">
+    <row r="30" ht="17.25" customHeight="1" spans="2:10">
       <c r="B30" s="17"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2270,7 +2267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:12">
+    <row r="31" ht="17.25" customHeight="1" spans="2:10">
       <c r="B31" s="17" t="s">
         <v>86</v>
       </c>
@@ -2297,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:12">
+    <row r="32" ht="17.25" customHeight="1" spans="2:10">
       <c r="B32" s="17"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2694,7 +2691,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="6"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="15" t="s">
+      <c r="H52" s="21" t="s">
         <v>137</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -2705,38 +2702,38 @@
       </c>
     </row>
     <row r="53" ht="17.25" spans="2:10">
-      <c r="B53" s="17"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="5"/>
+      <c r="B53" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" s="16"/>
       <c r="H53" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J53" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" ht="17.25" spans="2:10">
-      <c r="B54" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="6"/>
       <c r="G54" s="16"/>
       <c r="H54" s="15" t="s">
         <v>143</v>
@@ -2745,14 +2742,14 @@
         <v>144</v>
       </c>
       <c r="J54" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="17.25" spans="2:10">
-      <c r="B55" s="19"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="6"/>
       <c r="G55" s="16"/>
       <c r="H55" s="15" t="s">
@@ -2762,43 +2759,43 @@
         <v>146</v>
       </c>
       <c r="J55" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" spans="2:10">
+      <c r="B56" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" s="12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" ht="17.25" spans="2:10">
-      <c r="B56" s="20"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="16"/>
+      <c r="E56" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="G56" s="22"/>
       <c r="H56" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J56" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" ht="17.25" spans="2:10">
-      <c r="B57" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C57" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G57" s="21"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="22"/>
       <c r="H57" s="15" t="s">
         <v>151</v>
       </c>
@@ -2806,7 +2803,7 @@
         <v>152</v>
       </c>
       <c r="J57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" ht="17.25" spans="2:10">
@@ -2815,7 +2812,7 @@
       <c r="D58" s="12"/>
       <c r="E58" s="12"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="21"/>
+      <c r="G58" s="22"/>
       <c r="H58" s="15" t="s">
         <v>153</v>
       </c>
@@ -2823,7 +2820,7 @@
         <v>154</v>
       </c>
       <c r="J58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" ht="17.25" spans="2:10">
@@ -2832,7 +2829,7 @@
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="21"/>
+      <c r="G59" s="22"/>
       <c r="H59" s="15" t="s">
         <v>155</v>
       </c>
@@ -2840,16 +2837,16 @@
         <v>156</v>
       </c>
       <c r="J59" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" ht="17.25" spans="2:10">
-      <c r="B60" s="19"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="21"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="22"/>
       <c r="H60" s="15" t="s">
         <v>157</v>
       </c>
@@ -2857,23 +2854,6 @@
         <v>158</v>
       </c>
       <c r="J60" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" ht="17.25" spans="2:10">
-      <c r="B61" s="20"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J61" s="5">
         <v>4</v>
       </c>
     </row>
@@ -2891,9 +2871,9 @@
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="B44:B47"/>
     <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B56:B60"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C20"/>
@@ -2905,9 +2885,9 @@
     <mergeCell ref="C41:C43"/>
     <mergeCell ref="C44:C47"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C60"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D20"/>
@@ -2919,9 +2899,9 @@
     <mergeCell ref="D41:D43"/>
     <mergeCell ref="D44:D47"/>
     <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="D56:D60"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E20"/>
@@ -2933,9 +2913,9 @@
     <mergeCell ref="E41:E43"/>
     <mergeCell ref="E44:E47"/>
     <mergeCell ref="E48:E49"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="E56:E60"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F20"/>
@@ -2947,9 +2927,9 @@
     <mergeCell ref="F41:F43"/>
     <mergeCell ref="F44:F47"/>
     <mergeCell ref="F48:F49"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="F57:F61"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="F56:F60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__enums__.xlsx
+++ b/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="153">
   <si>
     <t>##var</t>
   </si>
@@ -335,12 +335,6 @@
     <t>更多大肉</t>
   </si>
   <si>
-    <t>StartSpecialBullet</t>
-  </si>
-  <si>
-    <t>开局特殊子弹</t>
-  </si>
-  <si>
     <t>StartEnergy</t>
   </si>
   <si>
@@ -408,18 +402,6 @@
   </si>
   <si>
     <t>特殊礼包</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Enum.ELuckyGiftCostType</t>
-  </si>
-  <si>
-    <t>礼包付费方式</t>
-  </si>
-  <si>
-    <t>Ad</t>
-  </si>
-  <si>
-    <t>广告</t>
   </si>
   <si>
     <t>HuntingConfig.Enum.EQuestType</t>
@@ -1208,7 +1190,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1270,9 +1252,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -1597,7 +1576,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -2403,7 +2382,7 @@
         <v>103</v>
       </c>
       <c r="J37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" ht="17.25" customHeight="1" spans="2:10">
@@ -2420,7 +2399,7 @@
         <v>105</v>
       </c>
       <c r="J38" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="17.25" customHeight="1" spans="2:10">
@@ -2437,103 +2416,103 @@
         <v>107</v>
       </c>
       <c r="J39" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B40" s="17"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
+      <c r="B40" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="G40" s="7"/>
       <c r="H40" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J40" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B41" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>111</v>
-      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
       <c r="G41" s="7"/>
       <c r="H41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I41" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="J41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B42" s="19"/>
+      <c r="B42" s="20"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="7"/>
       <c r="H42" s="6" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>114</v>
       </c>
       <c r="J42" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1" spans="2:10">
+      <c r="B43" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B43" s="20"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
+      <c r="E43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="G43" s="7"/>
       <c r="H43" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J43" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B44" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
       <c r="G44" s="7"/>
       <c r="H44" s="6" t="s">
         <v>119</v>
@@ -2542,7 +2521,7 @@
         <v>120</v>
       </c>
       <c r="J44" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" spans="2:10">
@@ -2559,7 +2538,7 @@
         <v>122</v>
       </c>
       <c r="J45" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1" spans="2:10">
@@ -2576,153 +2555,153 @@
         <v>124</v>
       </c>
       <c r="J46" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B47" s="17"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" spans="2:10">
+      <c r="B47" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" s="5"/>
       <c r="H47" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J47" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" spans="2:10">
-      <c r="B48" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D48" s="5" t="b">
+    </row>
+    <row r="48" ht="17.25" spans="2:10">
+      <c r="B48" s="17"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J48" s="5">
         <v>1</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J48" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="17.25" customHeight="1" spans="2:10">
+    </row>
+    <row r="49" ht="17.25" spans="2:10">
       <c r="B49" s="17"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="6"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="6" t="s">
-        <v>129</v>
+      <c r="G49" s="5"/>
+      <c r="H49" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J49" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" spans="2:10">
+      <c r="B50" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" ht="17.25" spans="2:10">
-      <c r="B50" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="G50" s="16"/>
+      <c r="H50" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J50" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="51" ht="17.25" spans="2:10">
-      <c r="B51" s="17"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6" t="s">
-        <v>135</v>
+      <c r="G51" s="16"/>
+      <c r="H51" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J51" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="17.25" spans="2:10">
-      <c r="B52" s="17"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="21" t="s">
-        <v>137</v>
+      <c r="G52" s="16"/>
+      <c r="H52" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J52" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="53" ht="17.25" spans="2:10">
-      <c r="B53" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" s="10" t="b">
+      <c r="B53" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="D53" s="10" t="b">
+      <c r="D53" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G53" s="16"/>
+      <c r="F53" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G53" s="21"/>
       <c r="H53" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J53" s="5">
         <v>0</v>
@@ -2733,52 +2712,42 @@
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="16"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="21"/>
       <c r="H54" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J54" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="17.25" spans="2:10">
-      <c r="B55" s="20"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="16"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="21"/>
       <c r="H55" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J55" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="56" ht="17.25" spans="2:10">
-      <c r="B56" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C56" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G56" s="22"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="21"/>
       <c r="H56" s="15" t="s">
         <v>149</v>
       </c>
@@ -2786,16 +2755,16 @@
         <v>150</v>
       </c>
       <c r="J56" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" ht="17.25" spans="2:10">
-      <c r="B57" s="19"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="22"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="21"/>
       <c r="H57" s="15" t="s">
         <v>151</v>
       </c>
@@ -2803,62 +2772,11 @@
         <v>152</v>
       </c>
       <c r="J57" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" ht="17.25" spans="2:10">
-      <c r="B58" s="19"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J58" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" ht="17.25" spans="2:10">
-      <c r="B59" s="19"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="J59" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" ht="17.25" spans="2:10">
-      <c r="B60" s="20"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="J60" s="5">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="66">
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B14"/>
@@ -2867,13 +2785,12 @@
     <mergeCell ref="B25:B28"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B31:B35"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B47:B49"/>
     <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="B53:B57"/>
     <mergeCell ref="C4:C9"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="C15:C20"/>
@@ -2881,13 +2798,12 @@
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="C31:C35"/>
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C47:C49"/>
     <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C53:C57"/>
     <mergeCell ref="D4:D9"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="D15:D20"/>
@@ -2895,13 +2811,12 @@
     <mergeCell ref="D25:D28"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D31:D35"/>
-    <mergeCell ref="D36:D40"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D47:D49"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="D53:D57"/>
     <mergeCell ref="E4:E9"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="E15:E20"/>
@@ -2909,13 +2824,12 @@
     <mergeCell ref="E25:E28"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="E31:E35"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E44:E47"/>
-    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="E47:E49"/>
     <mergeCell ref="E50:E52"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="E53:E57"/>
     <mergeCell ref="F4:F9"/>
     <mergeCell ref="F10:F14"/>
     <mergeCell ref="F15:F20"/>
@@ -2923,13 +2837,12 @@
     <mergeCell ref="F25:F28"/>
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="F31:F35"/>
-    <mergeCell ref="F36:F40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="F36:F39"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="F47:F49"/>
     <mergeCell ref="F50:F52"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="F53:F57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
